--- a/upwork_sample.xlsx
+++ b/upwork_sample.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nikun\OneDrive\Documents\GitHub\company-programs-upwork_supplier_program_new\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nikun\OneDrive\Documents\GitHub\company-programs-upwork_supplier_program\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8392BAC8-958C-46FA-A16C-A088DC04D8F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30A94105-3C27-4D48-AE7F-EA1C7BE89272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EC86652E-55B6-AF4A-89A1-6344CE3DA5F9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EC86652E-55B6-AF4A-89A1-6344CE3DA5F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -98,11 +98,11 @@
     <t>Sample Status</t>
   </si>
   <si>
+    <t>Infrared Thermometer</t>
+  </si>
+  <si>
     <t>Just like model listing.
-Quantity: 500</t>
-  </si>
-  <si>
-    <t>yoga mat</t>
+Quantity: 1000</t>
   </si>
 </sst>
 </file>
@@ -661,33 +661,33 @@
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E2" s="6"/>
       <c r="F2" s="9" t="str">
-        <f>HYPERLINK("https://www.amazon.com/dp/B092Y63TWF","test")</f>
+        <f>HYPERLINK("https://www.amazon.com/dp/B0C3B2VZLJ","test")</f>
         <v>test</v>
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
       <c r="I2" s="9" t="str">
-        <f>HYPERLINK("https://www.amazon.com/dp/B092Y63TWF","link")</f>
+        <f>HYPERLINK("https://www.amazon.com/dp/B0C3B2VZLJ","link")</f>
         <v>link</v>
       </c>
       <c r="J2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="6">
+        <v>1000</v>
+      </c>
+      <c r="L2" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="6">
-        <v>500</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>21</v>
-      </c>
       <c r="M2" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N2" s="8">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="O2" s="8"/>
       <c r="P2" s="8"/>
@@ -756,6 +756,5 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/upwork_sample.xlsx
+++ b/upwork_sample.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nikun\OneDrive\Documents\GitHub\company-programs-upwork_supplier_program_new\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nikun\OneDrive\Documents\GitHub\company-programs-upwork_supplier_program_latest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8392BAC8-958C-46FA-A16C-A088DC04D8F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9EEFC8-DD25-4F9B-9C49-C9BE835BE66C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EC86652E-55B6-AF4A-89A1-6344CE3DA5F9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EC86652E-55B6-AF4A-89A1-6344CE3DA5F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -99,10 +99,10 @@
   </si>
   <si>
     <t>Just like model listing.
-Quantity: 500</t>
-  </si>
-  <si>
-    <t>yoga mat</t>
+Quantity: 1000</t>
+  </si>
+  <si>
+    <t>mechanical keyboard rgb</t>
   </si>
 </sst>
 </file>
@@ -665,20 +665,20 @@
       </c>
       <c r="E2" s="6"/>
       <c r="F2" s="9" t="str">
-        <f>HYPERLINK("https://www.amazon.com/dp/B092Y63TWF","test")</f>
+        <f>HYPERLINK("https://www.amazon.com/dp/B01NAI2TXC","test")</f>
         <v>test</v>
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
       <c r="I2" s="9" t="str">
-        <f>HYPERLINK("https://www.amazon.com/dp/B092Y63TWF","link")</f>
+        <f>HYPERLINK("https://www.amazon.com/dp/B01NAI2TXC","link")</f>
         <v>link</v>
       </c>
       <c r="J2" s="6" t="s">
         <v>20</v>
       </c>
       <c r="K2" s="6">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="L2" s="10" t="s">
         <v>21</v>
@@ -687,7 +687,7 @@
         <v>21</v>
       </c>
       <c r="N2" s="8">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="O2" s="8"/>
       <c r="P2" s="8"/>
@@ -756,6 +756,5 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>